--- a/reports/빅딜/history/2026-09-27/빅딜_league_mgf_report.xlsx
+++ b/reports/빅딜/history/2026-09-27/빅딜_league_mgf_report.xlsx
@@ -78,7 +78,7 @@
     <t>Scania 2</t>
   </si>
   <si>
-    <t>850</t>
+    <t>851</t>
   </si>
   <si>
     <t>38위</t>
